--- a/jpcore-r4b/develop/CodeSystem-jp-microbiology-category-cs.xlsx
+++ b/jpcore-r4b/develop/CodeSystem-jp-microbiology-category-cs.xlsx
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
